--- a/static/data/exports/Retro_JK_AE_2024.xlsx
+++ b/static/data/exports/Retro_JK_AE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_JK_AE_2024.xlsx
+++ b/static/data/exports/Retro_JK_AE_2024.xlsx
@@ -31531,20 +31531,20 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>1932428</v>
+        <v>1932429</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Mohsin Shafqat Mir</t>
+          <t>Nizamuddin Bhat</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>24854</v>
+        <v>24808</v>
       </c>
       <c r="E502" t="n">
         <v>839</v>
@@ -31568,12 +31568,12 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Mohsin Shafqat Mir</t>
+          <t>Nizamuddin Bhat</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q502" t="b">
@@ -31593,20 +31593,20 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1932429</v>
+        <v>1932428</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Nizamuddin Bhat</t>
+          <t>Mohsin Shafqat Mir</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>24808</v>
+        <v>24854</v>
       </c>
       <c r="E503" t="n">
         <v>839</v>
@@ -31630,12 +31630,12 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Nizamuddin Bhat</t>
+          <t>Mohsin Shafqat Mir</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="Q503" t="b">
